--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136327534</v>
       </c>
       <c r="B2" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136191691</v>
       </c>
       <c r="B3" t="n">
-        <v>97615</v>
+        <v>97618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136191690</v>
       </c>
       <c r="B4" t="n">
-        <v>93108</v>
+        <v>93111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136327534</v>
       </c>
       <c r="B2" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136191691</v>
       </c>
       <c r="B3" t="n">
-        <v>97618</v>
+        <v>97619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136191690</v>
       </c>
       <c r="B4" t="n">
-        <v>93111</v>
+        <v>93112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136327534</v>
       </c>
       <c r="B2" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136191691</v>
       </c>
       <c r="B3" t="n">
-        <v>97619</v>
+        <v>97624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136191690</v>
       </c>
       <c r="B4" t="n">
-        <v>93112</v>
+        <v>93117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136191688</v>
       </c>
       <c r="B5" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136191692</v>
       </c>
       <c r="B6" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136191694</v>
       </c>
       <c r="B7" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>136327601</v>
       </c>
       <c r="B8" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136327534</v>
       </c>
       <c r="B2" t="n">
-        <v>96782</v>
+        <v>96784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136191691</v>
       </c>
       <c r="B3" t="n">
-        <v>97624</v>
+        <v>97626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136191690</v>
       </c>
       <c r="B4" t="n">
-        <v>93117</v>
+        <v>93119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33141-2026 artfynd.xlsx
+++ b/artfynd/A 33141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136327534</v>
       </c>
       <c r="B2" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
